--- a/knowledge/contacts.xlsx
+++ b/knowledge/contacts.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:I71"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,43 +407,1799 @@
         <v>Role</v>
       </c>
       <c r="C1" t="str">
-        <v>WhatsApp / Phone</v>
+        <v>Phone Number</v>
       </c>
       <c r="D1" t="str">
+        <v>Department</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Classes / Subjects</v>
+      </c>
+      <c r="F1" t="str">
+        <v>LID ID</v>
+      </c>
+      <c r="G1" t="str">
         <v>Handles</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Employment Type</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Presence / Availability Notes</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Mr. Yeghia</v>
+        <v>Ms. Houry Ohanian</v>
       </c>
       <c r="B2" t="str">
-        <v>IT Manager</v>
+        <v>Head of Department</v>
       </c>
       <c r="C2" t="str">
-        <v>96170688510</v>
+        <v>03/635479 / 01/878790</v>
       </c>
       <c r="D2" t="str">
-        <v>All IT issues, ESkool admin, network, hardware</v>
+        <v>KG</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v>61933529088184@lid</v>
+      </c>
+      <c r="G2" t="str">
+        <v>KG Department Head</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I2" t="str">
+        <v>KG HoD — administrative role</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v/>
+        <v>Ms. Talin Arabian</v>
       </c>
       <c r="B3" t="str">
-        <v/>
+        <v>Teacher</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>70/332609</v>
       </c>
       <c r="D3" t="str">
-        <v>Add more contacts here</v>
+        <v>KG</v>
+      </c>
+      <c r="E3" t="str">
+        <v>PRE-KG Homeroom</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Ms. Nayiri Kazdjian</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C4" t="str">
+        <v>03/372569</v>
+      </c>
+      <c r="D4" t="str">
+        <v>KG</v>
+      </c>
+      <c r="E4" t="str">
+        <v>PRE-KG Homeroom</v>
+      </c>
+      <c r="F4" t="str">
+        <v>221852274307227@lid</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Also listed as Nayiri Israbian in KG schedule files</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Ms. Dzovag Aynilian</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C5" t="str">
+        <v>76/472584</v>
+      </c>
+      <c r="D5" t="str">
+        <v>KG</v>
+      </c>
+      <c r="E5" t="str">
+        <v>KG1 Homeroom | Bible KG1-KG3 | Science KG1 | Robotics KG1-KG3 | Playtime KG1</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Ms. Caroline Missisian</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C6" t="str">
+        <v>70/591319</v>
+      </c>
+      <c r="D6" t="str">
+        <v>KG</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Armenian Pre-KG KG1 KG2 | Sports KG1 KG2 KG3</v>
+      </c>
+      <c r="F6" t="str">
+        <v>229626299338981@lid</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Ms. Rita Rizk</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C7" t="str">
+        <v>76/058061 / 01/682853</v>
+      </c>
+      <c r="D7" t="str">
+        <v>KG</v>
+      </c>
+      <c r="E7" t="str">
+        <v>KG3-A Homeroom | Arabic KG1 KG2 KG3</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Ms. Talar Kademian</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C8" t="str">
+        <v>70/054306</v>
+      </c>
+      <c r="D8" t="str">
+        <v>KG</v>
+      </c>
+      <c r="E8" t="str">
+        <v>KG3-B Homeroom | Math KG1 KG2 KG3</v>
+      </c>
+      <c r="F8" t="str">
+        <v>34359839088805@lid</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Ms. Mary Mertkhanian</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C9" t="str">
+        <v>03/029627</v>
+      </c>
+      <c r="D9" t="str">
+        <v>KG</v>
+      </c>
+      <c r="E9" t="str">
+        <v>KG2 Assistant</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I9" t="str">
+        <v>KG2 Assistant</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Ms. Margo Kordahi</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C10" t="str">
+        <v>03/854304</v>
+      </c>
+      <c r="D10" t="str">
+        <v>KG + Elementary</v>
+      </c>
+      <c r="E10" t="str">
+        <v>English KG3 Grade 1 | Bible Grades 1 2 3</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Ms. Mireille Mardirossian</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C11" t="str">
+        <v>03/476171</v>
+      </c>
+      <c r="D11" t="str">
+        <v>KG + Elementary</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Armenian KG3 | Armenian Grades 1 2 3</v>
+      </c>
+      <c r="F11" t="str">
+        <v>65378126442619@lid</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Ms. Lena Nader</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C12" t="str">
+        <v>03/844162 / 01/684104</v>
+      </c>
+      <c r="D12" t="str">
+        <v>KG</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Drama KG3 | English KG1 KG2 | Science Pre-KG KG2 KG3</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Ms. Jennifer Degermenjian</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C13" t="str">
+        <v>76/149391</v>
+      </c>
+      <c r="D13" t="str">
+        <v>KG</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Math Pre-KG | Arts &amp; Crafts KG1-KG3 | Movement KG1 KG2</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I13" t="str">
+        <v>On campus: Mon, Wed, Fri — full days only</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Ms. Caroline Oughourlian</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C14" t="str">
+        <v>03/525996</v>
+      </c>
+      <c r="D14" t="str">
+        <v>KG</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Music KG1 KG2 KG3</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I14" t="str">
+        <v>On campus: Tue 08:00–11:30 | Thu 08:00–12:10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Ms. Ani Boghossian</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C15" t="str">
+        <v>79/314188</v>
+      </c>
+      <c r="D15" t="str">
+        <v>KG Special Department</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Child Education Pre-KG KG1 KG2 KG3 | Story Telling KG1 | Playtime KG1</v>
+      </c>
+      <c r="F15" t="str">
+        <v>157397800722677@lid</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I15" t="str">
+        <v>On campus: Mon 08:00–14:00 | Tue 08:00–14:00 | Thu 08:00–14:00. NOT present Wed or Fri.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Mr. Gregoire Toranian</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Psychologist / KG Sp. Dept Coord.</v>
+      </c>
+      <c r="C16" t="str">
+        <v>70/267675</v>
+      </c>
+      <c r="D16" t="str">
+        <v>KG Special Department</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I16" t="str">
+        <v>KG Psychologist — verify days present</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Ms. Patil Balabanian</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C17" t="str">
+        <v>70/148202</v>
+      </c>
+      <c r="D17" t="str">
+        <v>KG + Elementary</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Dance KG1-KG3 Grades 1-6</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I17" t="str">
+        <v>On campus: Thu &amp; Fri full day only</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Mr. Ghazar Keoshgerian</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C18" t="str">
+        <v>71/923440</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Elementary</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Music Grades 1-6</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I18" t="str">
+        <v>On campus: Tue 10:30–12:30 | Thu 10:30–12:30 | Fri 10:30–14:00</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Ms. Maral Manisalian</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C19" t="str">
+        <v>71/546214</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Elementary</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Art / Drawing Grades 1-6</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I19" t="str">
+        <v>On campus: Mon &amp; Tue 08:00–10:15 only (first 3 periods)</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Mr. Khachig Seropian</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C20" t="str">
+        <v>70/218901</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Sports — All School</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Sports Grades 1-11</v>
+      </c>
+      <c r="F20" t="str">
+        <v>131494869741568@lid</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Sports — all school</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Ms. Kawkab Haddad</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C21" t="str">
+        <v>03/825317 / 01/683556</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Elementary</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Arabic Grades 1 2 3</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Ms. Maggie Boghossian</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C22" t="str">
+        <v>70/153961 / 04/920004</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Elementary</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Arabic Grades 4 5 6</v>
+      </c>
+      <c r="F22" t="str">
+        <v>157397800722677@lid</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Mrs. Markrid Margossian</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C23" t="str">
+        <v>03/045624</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Elementary</v>
+      </c>
+      <c r="E23" t="str">
+        <v>English Grades 2 3 4</v>
+      </c>
+      <c r="F23" t="str">
+        <v>72709534953547@lid</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Ms. Tamar Gumushian</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Teacher + Librarian</v>
+      </c>
+      <c r="C24" t="str">
+        <v>71/747010</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Elementary + Library</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Science Grades 1 2 | Bible Grades 4 5 6</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I24" t="str">
+        <v>On campus: full day 08:00–14:00. When no class, she is at the library.</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Ms. Sella Moughalian</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C25" t="str">
+        <v>71/301580 / 01/692517</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Elementary</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Math Grades 1 2 3 | Science Grades 3 4 5 6</v>
+      </c>
+      <c r="F25" t="str">
+        <v>94772849037513@lid</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Ms. Maral Avedissian</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C26" t="str">
+        <v>76/798006 / 01/562033</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Elementary + Intermediate</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Math Grades 4 5 6 7</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Ms. Vana Zeitounian</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C27" t="str">
+        <v>71/501800</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Elementary</v>
+      </c>
+      <c r="E27" t="str">
+        <v>French Grades 1-6 | Armenian History Grades 1-4</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I27" t="str">
+        <v>On campus: Mon 09:30–12:10 | Wed 09:30–12:10 | Fri 08:45–12:10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Ms. Marina Hamamjian</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C28" t="str">
+        <v>70/832204</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Elementary + Intermediate</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Armenian Grades 5 6 7 | Armenian History Grades 5 6 7</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I28" t="str">
+        <v>On campus: Mon–Fri 08:00–10:15 only (first 3 periods)</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Ms. Rima Cholakian</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C29" t="str">
+        <v>03/981787 / 04/870865</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Elementary + American Program</v>
+      </c>
+      <c r="E29" t="str">
+        <v>English Grades 5 6 | Social Studies (AP) Grades 7-12</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Mrs. Maria Guiragossian</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Elementary HoD + Teacher</v>
+      </c>
+      <c r="C30" t="str">
+        <v>03/694532</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Elementary HoD + Intermediate</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Math Grade 8</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Elementary Head of Department</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Ms. Haverj Kojaoghlanian</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Psychologist</v>
+      </c>
+      <c r="C31" t="str">
+        <v>03/817251</v>
+      </c>
+      <c r="D31" t="str">
+        <v>American Program + Counsellor + Elementary</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Armenian Grade 4 | Psychology (AP) Grades 7-10 12SE</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Also known as Haverj Shekherdemian</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Comes specific days — verify schedule</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Ms. Heghnar</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v>Elementary</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Robotics Grades 1-6</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Elementary Robotics teacher</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I32" t="str">
+        <v>On campus: Thu only, all day 08:00–14:00</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Ms. Hamesd Boyadjian</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Head of Special Ed Dept</v>
+      </c>
+      <c r="C33" t="str">
+        <v>76/652468 / 01/871423</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Special Ed — Elementary &amp; Intermediate</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Support/Pull-out Arabic Grades 5 8 9</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Head of Special Education Department</v>
+      </c>
+      <c r="H33" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Special Ed HoD</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Ms. Carine Abaklian</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C34" t="str">
+        <v>03/849471</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Special Ed — Elementary</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Support Arabic Grades 1-4 | Pull-out Arabic Grades 1-4</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Special Ed</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Ms. Nayiri Lousinian</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C35" t="str">
+        <v>71/741925</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Special Ed — Elementary + Intermediate</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Pull-out/Support English Grade 1 | Arabic Grades 5-7 | Science Grades 1-6</v>
+      </c>
+      <c r="F35" t="str">
+        <v>90937510346839@lid</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Special Ed</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Ms. Patil Kazanjian</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C36" t="str">
+        <v>71/856770</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Special Ed — Elementary</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Pull-out/Support Math Grades 4 5 6</v>
+      </c>
+      <c r="F36" t="str">
+        <v>24760637513898@lid</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I36" t="str">
+        <v>On campus: Mon NOT available | Tue 07:15–13:15 | Wed 08:00–10:45 | Thu 08:00–14:00 | Fri 08:00–13:10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Ms. Melissa Mardikian</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C37" t="str">
+        <v>76/580653</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Special Ed — Elementary</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Pull-out/Support Math Grades 1 2 3</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I37" t="str">
+        <v>Special Ed</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Ms. Christine Torossian</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C38" t="str">
+        <v>81/336605</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Special Ed — Elementary</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Pull-out/Support English Grades 2-6</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Special Ed</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Ms. Mariebelle Mansour</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C39" t="str">
+        <v>71/090133</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Elementary + Intermediate + Special Ed</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Social Studies (Geography History Civics) Grades 5-8 | Special Ed Bio/Chem Pull-out Grades 7-9</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Special Ed + Social Studies</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Mr. Hagop Chakmakian</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C40" t="str">
+        <v>70/452014</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Special Ed — Intermediate</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Pull-out/Support Math Grades 7-9 | Pull-out/Support Physics Grades 7-9</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Special Ed</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Ms. Varty Salkhanian</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C41" t="str">
+        <v>78/920637</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Intermediate</v>
+      </c>
+      <c r="E41" t="str">
+        <v>English Grades 7 8 9</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Ms. Lena Titizian</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C42" t="str">
+        <v>70/047808 / 09/221624</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Intermediate</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Arabic Grades 7 8 9</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Also listed as Lena Azad in schedules</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Ms. Maral Haidostian</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C43" t="str">
+        <v>70/134453 / 01/739375</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Intermediate + Secondary</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Bible Grades 7-11</v>
+      </c>
+      <c r="F43" t="str">
+        <v>138650318860529@lid</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I43" t="str">
+        <v>On campus: Tue &amp; Thu 08:00–12:10 only</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Ms. Rita Avedanian</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C44" t="str">
+        <v>76/993713</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Intermediate + Secondary</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Chemistry Grades 7 8 11H 12SE | Biology Grades 7 8 10 | Physics Grades 7 8 11H</v>
+      </c>
+      <c r="F44" t="str">
+        <v>171979231510541@lid</v>
+      </c>
+      <c r="H44" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I44" t="str">
+        <v>On campus: Mon 08:00–11:30 | Tue 08:00–14:00 | Wed 08:00–12:10 | Thu 08:00–14:00 | Fri 10:30–14:00</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Ms. Tania El Khoury</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C45" t="str">
+        <v>70/320111</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Secondary</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Arabic Grades 10 11 (all sections) 12 (all sections)</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Ms. Houry Kevorkian</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C46" t="str">
+        <v>03/334916</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Secondary</v>
+      </c>
+      <c r="E46" t="str">
+        <v>English Grades 12SE 12LS | Sociology Grade 12SE | Sociology Grade 11H</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I46" t="str">
+        <v>On campus: Mon 10:30–14:00 | Thu 08:00–10:15</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Ms. Aline Kevorkian</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C47" t="str">
+        <v>03/796074</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Secondary</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Economics Grades 11H 12SE</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I47" t="str">
+        <v>On campus: Mon 08:00–10:15 | Wed 08:00–10:15</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Ms. Maria Ounjian</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C48" t="str">
+        <v>03/408462 / 04/418396</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Secondary</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Biology Grades 11S 11LS 12LS</v>
+      </c>
+      <c r="F48" t="str">
+        <v>225236708536503@lid</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I48" t="str">
+        <v>On campus: Mon 08:00–09:30 | Wed 10:30–13:15 | Fri 07:30–09:30</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Ms. Nora Terzian</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Biology Coordinator + Teacher</v>
+      </c>
+      <c r="C49" t="str">
+        <v>03/173826 / 04/712864</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Biology Department</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Biology Grades 9 11H 12SE</v>
+      </c>
+      <c r="F49" t="str">
+        <v>143911653781623@lid</v>
+      </c>
+      <c r="G49" t="str">
+        <v>Biology Department Coordinator</v>
+      </c>
+      <c r="H49" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I49" t="str">
+        <v>On campus: Mon, Wed, Thu, Fri. NOT present on Tuesdays.</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Mr. Viken Dishgekenian</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C50" t="str">
+        <v>70/236012 / 01/871711</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Intermediate + Secondary</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Chemistry Grades 9 10 11S 12LS | Physics Grade 9</v>
+      </c>
+      <c r="F50" t="str">
+        <v>273890081292395@lid</v>
+      </c>
+      <c r="H50" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Mr. Vicken Koujanian</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Physics Coordinator + Teacher</v>
+      </c>
+      <c r="C51" t="str">
+        <v>03/467883</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Physics Department + Secondary</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Physics Grades 10 11S 12LS 12SE | Math Grades 11S 12SE 12LS</v>
+      </c>
+      <c r="F51" t="str">
+        <v>86719768588459@lid</v>
+      </c>
+      <c r="G51" t="str">
+        <v>Physics Department Coordinator</v>
+      </c>
+      <c r="H51" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I51" t="str">
+        <v>Physics Coordinator</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Mr. Atam Tazian</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C52" t="str">
+        <v>03/328749 / 01/243282</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Secondary</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Math Grade 12 sections LS and SE</v>
+      </c>
+      <c r="H52" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I52" t="str">
+        <v>On campus: Mon 10:30–13:30 | Wed 08:00–09:30 | Fri 08:00–10:15</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Mr. Jano Baghboudarian</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Math Coordinator + Teacher</v>
+      </c>
+      <c r="C53" t="str">
+        <v>03/966712</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Math Department (All School)</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Math Grades 10 11S</v>
+      </c>
+      <c r="F53" t="str">
+        <v>262581583405299@lid</v>
+      </c>
+      <c r="G53" t="str">
+        <v>Math Department Coordinator (All School)</v>
+      </c>
+      <c r="H53" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I53" t="str">
+        <v>On campus: Mon 07:15–10:15 | Tue 08:00–10:15 | Thu 10:30–12:10 | Fri 07:30–10:15</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Mr. Alfredo Dawlabani</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C54" t="str">
+        <v>78/948048</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Intermediate + Secondary</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Math Grades 9 11H</v>
+      </c>
+      <c r="H54" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I54" t="str">
+        <v>On campus: Mon 08:45–10:15 | Tue 08:00–08:45 | Wed 08:00–10:15 | Thu 08:00–10:15 | Fri from 07:30 (dept. meeting) then 08:00–08:45</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Mr. Jawad Mestrah</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C55" t="str">
+        <v>71/103338</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Secondary</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Robotics Grades 7 8 9 10 11H</v>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I55" t="str">
+        <v>Teaches Fridays only</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Mr. Ralph Ibrahim</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C56" t="str">
+        <v>76/110062</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Secondary + American Program</v>
+      </c>
+      <c r="E56" t="str">
+        <v>English Grades 10 11LS 11H | AP English Grades 7-12</v>
+      </c>
+      <c r="H56" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Ms. Cynthia Shaker</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C57" t="str">
+        <v>71/686877</v>
+      </c>
+      <c r="D57" t="str">
+        <v>American Program</v>
+      </c>
+      <c r="E57" t="str">
+        <v>AP Arabic Grades 7-12</v>
+      </c>
+      <c r="H57" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Miss Alik Stanboulian</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Nurse + Teacher</v>
+      </c>
+      <c r="C58" t="str">
+        <v>79/121772</v>
+      </c>
+      <c r="D58" t="str">
+        <v>American Program Health Education</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Health Education (AP) Grades 7-12</v>
+      </c>
+      <c r="F58" t="str">
+        <v>232379323023423@lid</v>
+      </c>
+      <c r="G58" t="str">
+        <v>Also school nurse</v>
+      </c>
+      <c r="H58" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I58" t="str">
+        <v>Also school nurse — not always in class</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Mr. Pascal Al Ferzly</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Social Studies Coordinator + Teacher</v>
+      </c>
+      <c r="C59" t="str">
+        <v>03/516968 / 09/860446</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Intermediate + Secondary</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Social Studies Arabic (History Civics Geography) Grades 9-12</v>
+      </c>
+      <c r="F59" t="str">
+        <v>101211038576701@lid</v>
+      </c>
+      <c r="G59" t="str">
+        <v>Social Studies Coordinator</v>
+      </c>
+      <c r="H59" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I59" t="str">
+        <v>On campus: Mon 08:00–11:25 | Tue full day</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Ms. Rozette Al Haddad</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Arabic Subject Coordinator</v>
+      </c>
+      <c r="C60" t="str">
+        <v>03/245721 / 07/735473</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Arabic Department</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v>Arabic Subject Coordinator</v>
+      </c>
+      <c r="H60" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I60" t="str">
+        <v>Arabic Coordinator — verify days</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Dr. Anny Joukoulian</v>
+      </c>
+      <c r="B61" t="str">
+        <v>English Department Coordinator</v>
+      </c>
+      <c r="C61" t="str">
+        <v>70/050429</v>
+      </c>
+      <c r="D61" t="str">
+        <v>English Department</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v>Comes on Mondays only</v>
+      </c>
+      <c r="H61" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I61" t="str">
+        <v>Comes on Mondays only</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Ms. Ani Manougian</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Armenian Subjects Coordinator + Teacher</v>
+      </c>
+      <c r="C62" t="str">
+        <v>03/779376 / 01/248308</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Armenian Department</v>
+      </c>
+      <c r="E62" t="str">
+        <v>Armenian Grades 8-11 | Armenian History Grades 8-11</v>
+      </c>
+      <c r="G62" t="str">
+        <v>Armenian Subjects Coordinator</v>
+      </c>
+      <c r="H62" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I62" t="str">
+        <v>On campus: Tue–Fri 08:00–14:00. NOT present on Mondays.</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Mrs. Maral Deyirmenjian</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Principal</v>
+      </c>
+      <c r="C63" t="str">
+        <v>03/501062 / 01/873150</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Office + Secondary Teacher</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Arabic Grades 10 11 12 (part-time)</v>
+      </c>
+      <c r="F63" t="str">
+        <v>27625296814177@lid</v>
+      </c>
+      <c r="G63" t="str">
+        <v>Principal</v>
+      </c>
+      <c r="H63" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I63" t="str">
+        <v>Full-time office staff — present all week</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Dr. Taline Messerlian</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Academic Director</v>
+      </c>
+      <c r="C64" t="str">
+        <v>71/647180</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Office</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v>253609782550529@lid</v>
+      </c>
+      <c r="G64" t="str">
+        <v>Academic Director</v>
+      </c>
+      <c r="H64" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I64" t="str">
+        <v>Full-time office staff — present all week</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Mr. Vicken Missisian</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Disciplinarian</v>
+      </c>
+      <c r="C65" t="str">
+        <v>71/061630</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Intermediate + Secondary</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v>229626299338981@lid</v>
+      </c>
+      <c r="G65" t="str">
+        <v>Disciplinarian</v>
+      </c>
+      <c r="H65" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I65" t="str">
+        <v>Full-time office staff — present all week</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Miss Barig Barsoumian</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Accountant</v>
+      </c>
+      <c r="C66" t="str">
+        <v>70/606774 / 04/411784</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Office</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v>Accountant</v>
+      </c>
+      <c r="H66" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I66" t="str">
+        <v>Full-time office staff — present all week</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Mrs. Asdghig Jerahian</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Government Relations</v>
+      </c>
+      <c r="C67" t="str">
+        <v>03/469200</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Office</v>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v>Government Relations</v>
+      </c>
+      <c r="H67" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I67" t="str">
+        <v>On campus: Tuesdays and Fridays only</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Mrs. Lara Karghayan</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Secretary</v>
+      </c>
+      <c r="C68" t="str">
+        <v>03/396562</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Office</v>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v>7031029243954@lid</v>
+      </c>
+      <c r="G68" t="str">
+        <v>Secretary</v>
+      </c>
+      <c r="H68" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I68" t="str">
+        <v>Full-time office staff — present all week</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Mrs. Tamar Ohanian</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Bookstore</v>
+      </c>
+      <c r="C69" t="str">
+        <v>71/254566 / 01/897707</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Bookstore</v>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v>94764292690015@lid</v>
+      </c>
+      <c r="G69" t="str">
+        <v>Bookstore</v>
+      </c>
+      <c r="H69" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I69" t="str">
+        <v>Full-time office staff — present all week</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Mr. Yeghia Boghossian</v>
+      </c>
+      <c r="B70" t="str">
+        <v>IT Manager + Teacher</v>
+      </c>
+      <c r="C70" t="str">
+        <v>70/688510</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Office + Intermediate/Secondary Teacher</v>
+      </c>
+      <c r="E70" t="str">
+        <v>AI &amp; Digital Literacy Grades 7-10 (AP) + Grade 11 Humanities</v>
+      </c>
+      <c r="F70" t="str">
+        <v>157397800722677@lid</v>
+      </c>
+      <c r="G70" t="str">
+        <v>CHS.ai admin / IT support / Access codes / ESkool issues support</v>
+      </c>
+      <c r="H70" t="str">
+        <v>Full-time</v>
+      </c>
+      <c r="I70" t="str">
+        <v>On campus: Mon, Wed, Thu, Fri. Not present Tuesdays. Teaches Wed only.</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Ms. Maria Aprahamian</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="C71" t="str">
+        <v>03/528162</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Secondary — American Program</v>
+      </c>
+      <c r="E71" t="str">
+        <v>SAT Preparation</v>
+      </c>
+      <c r="F71" t="str">
+        <v>11124099538964@lid</v>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v>Part-time</v>
+      </c>
+      <c r="I71" t="str">
+        <v>On campus: Mon only 11:30–14:00</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I71"/>
   </ignoredErrors>
 </worksheet>
 </file>